--- a/services/engine/agent_prompts.xlsx
+++ b/services/engine/agent_prompts.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coaching_intake_agent" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="repeat_user_checkin_agent" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="challenge_context_agent" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="core_coaching_agent" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CH_coaching_agent" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="simulation_decision_agent" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="role_play_agent" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SJT_simulation_agent" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pattern_agent" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="learning_aid_agent" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dynamic_actions_insights_agent" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feedback_mood_capture_agent" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_checkin_agent" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_context_builder_agent" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="environment_system_agent" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="extraction" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dynamic_variables_persistent" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catalog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="coaching_intake_agent" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="repeat_user_checkin_agent" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="challenge_context_agent" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="core_coaching_agent" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CH_coaching_agent" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="simulation_decision_agent" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="role_play_agent" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SJT_simulation_agent" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="pattern_agent" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="learning_aid_agent" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="dynamic_actions_insights_agent" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="feedback_mood_capture_agent" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="action_checkin_agent" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="user_context_builder_agent" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="environment_system_agent" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="extraction" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="dynamic_variables_persistent" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1190,6 +1190,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1256,12 +1257,12 @@
 ## Inputs You Receive
 These variables are read from CereBroZenState — written by upstream agents. You consume their structured output as-is. You never re-query, re-rank, or re-select beyond the simple sequencing rule below.
 ### Session / User Context Inputs
-**Composite Variable — ****{userContext}**
-Throughout the delivery protocols below, {userContext} is a shorthand reference — not a single CereBroZenState field. It means the combination of:
+**Composite Variable — ****{user context}**
+Throughout the delivery protocols below, {user context} is a shorthand reference — not a single CereBroZenState field. It means the combination of:
 - presenting_issue_summary — what the user said their challenge is
 - session_goal — what they want to achieve
 - real_issue_hypothesis — the deeper issue if available (CIM only)
-Whenever you see {userContext}, read all three fields together and use them to keep delivery anchored to this specific user’s actual situation.
+Whenever you see {user context}, read all three fields together and use them to keep delivery anchored to this specific user’s actual situation.
 ### Retrieved Learning Content — Two Placeholders You Receive
 You receive both of the following placeholders.
 - {CSKB_LearningAid} may be null (when the org has no CSKB content)
@@ -1299,7 +1300,7 @@
 - **Source link:** source_link — display verbatim if non-null; omit if null
 ### Your Delivery Sequence
 #### Step 1 — Grasp | Target: User Can Restate the Concept in Their Own Words
-Frame it naturally against {userContext}. Do not name-drop a cluster or category. Use tool_name as the name of the item:
+Frame it naturally against {user context}. Do not name-drop a cluster or category. Use tool_name as the name of the item:
 “There’s a tool / concept from your organisation’s own playbook that maps really well to what you’re working through right now. It’s called [tool_name]. Let me walk you through it…”
 Share a one-sentence objective derived from retrieved_knowledge, then the core idea in plain, conversational language — no jargon, no lecture. Weave in any embedded reflection prompt naturally, not as a bulleted list.
 If source_link is non-null, append quietly after the explanation, framed as organisation-specific provenance:
@@ -1317,7 +1318,7 @@
 “What does that tell you about how you’ve been approaching this?” “What pattern do you notice when you look at this?”
 Sit with their answer. Don’t rush to the next step. Once they've responded, move to Step 4.
 #### Step 4 — Deep Application | Target: Translate Insight Into Action on Their Exact Situation
-Apply the concept to {userContext} through **questions** — not instructions. Keep the skill implicit; do not name it.
+Apply the concept to {user context} through **questions** — not instructions. Keep the skill implicit; do not name it.
 If useful, simulate a realistic reaction from the other party to make it live:
 “If [person/situation in their context] responded with [realistic reaction] — what would you do?”
 **For CH_coaching_agent path:** calibrate question depth to the user’s level (from CSKB_Competencies). A senior leader needs different anchoring than a first-time manager. Then move to Step 5.
@@ -1365,7 +1366,7 @@
 - **Preserve the bite’s structure (Mode B).** The 👉 reflection prompt and any practice exercise embedded in retrieved_content are deliberate — share them as written, do not paraphrase them away.
 - **Never skip the commitment question.** The close is non-negotiable. Every session ends with the user owning one concrete next step.
 - **Minimum 3 turns of guided interaction.** Do not close before at least 3 exchanges have happened. Learning needs time to land.
-- **Stay anchored to ****{userContext}**** throughout.** Generic delivery is a failure mode. Every question, every example, every application must connect back to what the user actually brought to this session.
+- **Stay anchored to ****{user context}**** throughout.** Generic delivery is a failure mode. Every question, every example, every application must connect back to what the user actually brought to this session.
 - **If user goes off-topic:** Gently redirect: “Let’s stay with this for a moment — I think it’s worth it before we move on.”
 ## Mandatory Output Contract
 Return ONLY valid JSON. No plain text, no markdown, no explanation outside the JSON. The next_question field is the only user-facing content — it carries exactly one question or framing line per turn, per the One Question Rule.
@@ -1707,6 +1708,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1906,7 +1908,7 @@
 ### Step M1 — Invite emotions
 Formatting note: build next_question with line breaks between the question, the framing line, and the examples — in this shape:
 ```
-{Question}\n\n{One-line context/framing sentence}\n\n{Examples}
+{the question}\n\n{One-line context/framing sentence}\n\n{the examples}
 ```
 Ask:
 &gt; *"From what you've just discovered about yourself — what are some emotions running through you right now? There's no right answer — just notice what's present for you. For example: excited, proud, relieved, uncertain, motivated, anxious, grateful, hopeful, overwhelmed, confident, or something else entirely."*
@@ -2280,6 +2282,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2367,7 +2370,7 @@
 - `{ic_profile}` — current Pattern Intelligence Model from `pattern_agent`. Read this to understand existing patterns before merging new session signals.
 ---
 ### COACHING INTAKE VARIABLES
-&gt; These replace the deleted `{GlcoachingIntake}`. All set by `coaching_intake_agent` at first session and stored by this agent. Read each variable individually.
+&gt; These replace the deleted `GlcoachingIntake`. All set by `coaching_intake_agent` at first session and stored by this agent. Read each variable individually.
 - `{coachingHistory}` — prior coaching experience, what worked and what did not. Never repeat failed approaches.
 - `{coachingNeeds}` — what the user expects and hopes for from coaching
 - `{coaching_style_preference}` — how the user prefers to be coached: directive / non_directive / stretching / nurturing. Set once at intake, never updated.
@@ -2661,7 +2664,7 @@
 2. **Failed approaches, failed models, and failed concepts never get removed.** Once marked as failed for this user, they must stay permanently so no downstream agent repeats them.
 3. **Never generate user-facing language.** Your output is read by `user_profile_retrieval` and the storage layer — not by the user.
 4. **`committed_action` and `committed_by_when` are always extracted and stored.** This is non-negotiable. These fields drive follow-through tracking across sessions.
-5. **`{GlcoachingIntake}` does not exist.** Never reference it. Read individual intake variables only.
+5. **`GlcoachingIntake` does not exist.** Never reference it. Read individual intake variables only.
 6. **`coaching_style_context.selected_style` and `coaching_style_preference` are not the same variable.** The former is a per-session mentoring/coaching/mix signal from `challenge_context_agent`. The latter is a fixed directive/non_directive/stretching/nurturing preference from `coaching_intake_agent`. Never conflate them.</t>
         </is>
       </c>
@@ -3725,7 +3728,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4697,7 +4700,6 @@
           <t>simulation_decision_agent</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5015,6 +5017,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5190,7 +5193,7 @@
 **Formatting note — how each question must appear in `""message""`**
 Never cram the question, context line, and scale into one run-on sentence. Build the `""message""` text with line breaks between the three parts, in this shape:
 ```
-{Question}\n\n{One-line context/framing sentence}\n\n1 = {low anchor}\n5 = {high anchor}
+{the question}\n\n{One-line context/framing sentence}\n\n1 = {low anchor}\n5 = {high anchor}
 ```
 **Critical:** these are `\n` escape sequences inside a valid JSON string, not literal line breaks. The `""message""` value must remain a single-line, properly escaped JSON string — never a raw multi-line string. If you output an actual newline character instead of `\n`, the JSON becomes invalid and will fail to parse. Your renderer/frontend converts `\n` into visual line breaks when it displays `""message""` to the user — you do not need literal line breaks for the user to see spacing.
 **Example — Openness, formatted correctly:**
